--- a/templates/HEADWAY_INFRASTRUCTURE_v1.0.xlsx
+++ b/templates/HEADWAY_INFRASTRUCTURE_v1.0.xlsx
@@ -567,7 +567,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3. Row 3 contains an illustrative example row (marked with ID 'EXAMPLE_*'). Replace or delete before production use.</t>
+          <t>3. Row 3 contains a minimal valid baseline network for demonstration purposes. You may modify or replace it with your own railway data. The example is designed to load without validation errors.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>BLK_01, BLK_02</t>
+          <t>BLK_01</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1074,6 +1074,23 @@
       <c r="C3" s="10" t="inlineStr">
         <is>
           <t>BUFFER_STOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>ND_02</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Downstream endpoint</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>ENDPOINT</t>
         </is>
       </c>
     </row>

--- a/templates/HEADWAY_INFRASTRUCTURE_v1.0.xlsx
+++ b/templates/HEADWAY_INFRASTRUCTURE_v1.0.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StoppingPoints" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tunnels" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVSSections" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharedResourceGroups" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVSGeometry" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharedResourceGroups" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -593,73 +594,87 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. For multi-link signalling blocks or TVS sections, define spatial geometry intervals in the 'BlockGeometry' or 'TVSGeometry' worksheet with sequential numbering.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>WORKSHEET INVENTORY:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• Nodes: Network vertices representing switches, buffer stops, or boundaries</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• Tracks: Physical railway track lines</t>
+          <t>• Nodes: Network vertices representing switches, buffer stops, or boundaries</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>• TrackLinks: 1D continuous track segments connecting nodes</t>
+          <t>• Tracks: Physical railway track lines</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>• Stations: Passenger and operational stations</t>
+          <t>• TrackLinks: 1D continuous track segments connecting nodes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>• Platforms: Station passenger platforms along track links</t>
+          <t>• Stations: Passenger and operational stations</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>• StoppingPoints: Designated stopping points at platforms</t>
+          <t>• Platforms: Station passenger platforms along track links</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>• Tunnels: Tunnel structures encompassing TVS ventilation zones</t>
+          <t>• StoppingPoints: Designated stopping points at platforms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>• TVSSections: Tunnel Ventilation Sections (Mandatory single-train rule)</t>
+          <t>• Tunnels: Tunnel structures encompassing TVS ventilation zones</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>• TVSSections: Tunnel Ventilation Sections (Mandatory single-train rule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>• TVSGeometry: Multi-link spatial interval geometry for Tunnel Ventilation Sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>• SharedResourceGroups: Mutually exclusive shared conflict resources</t>
         </is>
@@ -676,18 +691,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,30 +720,15 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>LINK_ID</t>
+          <t>MAX_OCCUPANCY</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>START_OFFSET_M</t>
+          <t>HOLDING_SIGNAL_ID</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>END_OFFSET_M</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>MAX_OCCUPANCY</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
-        <is>
-          <t>HOLDING_SIGNAL_ID</t>
-        </is>
-      </c>
-      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>RELEASE_DELAY_S</t>
         </is>
@@ -755,30 +752,15 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>(Required)</t>
+          <t>(Optional)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>[m]</t>
+          <t>(Optional)</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>[m]</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>(Optional)</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>(Optional)</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>[s]</t>
         </is>
@@ -800,26 +782,15 @@
           <t>TRK_M1</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>LNK_01</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>300</v>
+      <c r="D3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>SIG_01</t>
+        </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>SIG_01</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -829,6 +800,102 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>TVS_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>SEQUENCE</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>LINK_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>START_OFFSET_M</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>END_OFFSET_M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>[m]</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>[m]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>TVS_01</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>LNK_01</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
